--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-107)_261026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-107)_261026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEB042C-975B-4AC6-8FC0-B462ACB959DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB0CAB2-8F1A-493E-9758-9E254160F3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="266">
   <si>
     <t>STT</t>
   </si>
@@ -763,6 +763,66 @@
   </si>
   <si>
     <t>VNET860879084174982</t>
+  </si>
+  <si>
+    <t>VNET860879084179452</t>
+  </si>
+  <si>
+    <t>VNET860879084181102</t>
+  </si>
+  <si>
+    <t>VNET860879084180799</t>
+  </si>
+  <si>
+    <t>VNET860879084175955</t>
+  </si>
+  <si>
+    <t>VNET860879084179155</t>
+  </si>
+  <si>
+    <t>VNET860879084180260</t>
+  </si>
+  <si>
+    <t>VNET860879084183330</t>
+  </si>
+  <si>
+    <t>VNET860879084178991</t>
+  </si>
+  <si>
+    <t>VNET860879084181714</t>
+  </si>
+  <si>
+    <t>VNET860879084179197</t>
+  </si>
+  <si>
+    <t>VNET860879084177118</t>
+  </si>
+  <si>
+    <t>VNET860879084174461</t>
+  </si>
+  <si>
+    <t>VNET860879084182118</t>
+  </si>
+  <si>
+    <t>VNET860879084180062</t>
+  </si>
+  <si>
+    <t>VNET860879084176037</t>
+  </si>
+  <si>
+    <t>VNET860879084180302</t>
+  </si>
+  <si>
+    <t>VNET860879084182266</t>
+  </si>
+  <si>
+    <t>VNET860879084175476</t>
+  </si>
+  <si>
+    <t>VNET860879084177381</t>
+  </si>
+  <si>
+    <t>VNET860879084178827</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1300,157 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1887,7 +2097,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="33">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
@@ -2051,15 +2261,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC994CF-10F2-4E75-9971-34AD9C75ED9B}">
-  <dimension ref="A1:B294"/>
+  <dimension ref="A1:F294"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="35" customWidth="1"/>
     <col min="2" max="2" width="26" style="35" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="34"/>
+    <col min="3" max="5" width="9.140625" style="34"/>
+    <col min="6" max="6" width="34" style="35" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
@@ -2067,181 +2279,244 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="57"/>
       <c r="B2" s="31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="37" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F3" s="35" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="37" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F4" s="35" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="37" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F5" s="35" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="37" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F6" s="35" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="37" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F7" s="35" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="37" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F8" s="35" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="37" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F9" s="35" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="37" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F10" s="35" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="37" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F11" s="35" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="37" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F12" s="35" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="37" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F13" s="35" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>42</v>
       </c>
       <c r="B14" s="37" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F14" s="35" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="37" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F15" s="35" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="30" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="37" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F16" s="35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>45</v>
       </c>
       <c r="B17" s="37" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F17" s="35" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="30" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="37" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F18" s="35" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
         <v>47</v>
       </c>
       <c r="B19" s="37" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F19" s="35" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>48</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F20" s="35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
         <v>49</v>
       </c>
       <c r="B21" s="37" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F21" s="35" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="37" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F22" s="35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="37" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F23" s="35" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
         <v>52</v>
       </c>
@@ -2249,7 +2524,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
         <v>53</v>
       </c>
@@ -2257,7 +2532,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
         <v>54</v>
       </c>
@@ -2265,7 +2540,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
         <v>55</v>
       </c>
@@ -2273,7 +2548,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
         <v>56</v>
       </c>
@@ -2281,7 +2556,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
         <v>57</v>
       </c>
@@ -2289,7 +2564,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
         <v>58</v>
       </c>
@@ -2297,7 +2572,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
         <v>59</v>
       </c>
@@ -2305,7 +2580,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
         <v>61</v>
       </c>
@@ -2937,36 +3212,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:B10">
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="duplicateValues" dxfId="7" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:B15">
-    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B17">
-    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:B20">
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:B26">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:B31">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-107)_261026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-107)_261026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB0CAB2-8F1A-493E-9758-9E254160F3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FD219F-5736-40FB-B337-F2EDB9D3C899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -1300,237 +1300,7 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
